--- a/history.xlsx
+++ b/history.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7703,6 +7703,2619 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>921</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC41" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE41" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC41" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" s="3" t="inlineStr"/>
+      <c r="BH41" s="3" t="inlineStr"/>
+      <c r="BI41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>4078</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>4567</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC42" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" s="2" t="inlineStr"/>
+      <c r="BH42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4281</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC43" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE43" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC43" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" s="3" t="inlineStr"/>
+      <c r="BH43" s="3" t="inlineStr"/>
+      <c r="BI43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>3334</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE44" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC44" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" s="2" t="inlineStr"/>
+      <c r="BH44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD45" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE45" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA45" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BB45" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BC45" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BD45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" s="3" t="inlineStr"/>
+      <c r="BH45" s="3" t="inlineStr"/>
+      <c r="BI45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>3491</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2418</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y46" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC46" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC46" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="2" t="inlineStr"/>
+      <c r="BH46" s="2" t="inlineStr"/>
+      <c r="BI46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4676</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>2072</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC47" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD47" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE47" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC47" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" s="3" t="inlineStr"/>
+      <c r="BH47" s="3" t="inlineStr"/>
+      <c r="BI47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>5867</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE48" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC48" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" s="2" t="inlineStr"/>
+      <c r="BH48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC49" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD49" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE49" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC49" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" s="3" t="inlineStr"/>
+      <c r="BH49" s="3" t="inlineStr"/>
+      <c r="BI49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>5883</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y50" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD50" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC50" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" s="2" t="inlineStr"/>
+      <c r="BH50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>3912</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>1244</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC51" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD51" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE51" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF51" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC51" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" s="3" t="inlineStr"/>
+      <c r="BH51" s="3" t="inlineStr"/>
+      <c r="BI51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y52" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC52" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC52" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="2" t="inlineStr"/>
+      <c r="BH52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC53" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD53" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE53" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC53" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" s="3" t="inlineStr"/>
+      <c r="BH53" s="3" t="inlineStr"/>
+      <c r="BI53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7714,7 +10327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E664"/>
+  <dimension ref="A1:E885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23000,6 +25613,5089 @@
         <v>0</v>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D665" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E665" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E666" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D667" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E667" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E668" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D669" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E670" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D671" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D673" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E673" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E674" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D675" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E675" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E676" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D677" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E677" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E678" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D679" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E679" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D681" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E682" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D683" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E684" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D685" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E685" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E686" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C687" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D687" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E687" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D689" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E689" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E690" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D691" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E691" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E692" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B693" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C693" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D693" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E693" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E694" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B695" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C695" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D695" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E695" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E696" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B697" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C697" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D697" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E697" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E698" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B699" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C699" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D699" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E699" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E700" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B701" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C701" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D701" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E701" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E702" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C703" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D703" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E703" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E704" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C705" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D705" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E706" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C707" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D707" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E707" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E708" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C709" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D709" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C711" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D711" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E711" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E712" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C713" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D713" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E713" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E714" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B715" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C715" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D715" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E715" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B717" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C717" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D717" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E717" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E718" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D719" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E719" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E720" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B721" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C721" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D721" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E721" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E722" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D723" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E723" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D725" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B727" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D727" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C729" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D729" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E729" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D731" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C733" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D733" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E734" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C735" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D735" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B737" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C737" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D737" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C739" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D739" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E739" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E740" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B741" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D741" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E741" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B743" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C743" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D743" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B745" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C745" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D745" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D747" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B749" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C749" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D749" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C751" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D751" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C753" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D753" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E753" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E754" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C755" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D755" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E755" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E756" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B757" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C757" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D757" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B759" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C759" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D759" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B761" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C761" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D761" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E761" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E762" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B763" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C763" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D763" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E763" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B765" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C765" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D765" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E765" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B767" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C767" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D767" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B769" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C769" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D769" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B771" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C771" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D771" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B773" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C773" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D773" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B775" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C775" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D775" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E775" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B777" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C777" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D777" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E777" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E778" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C779" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D779" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E779" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E780" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B781" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C781" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D781" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B783" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C783" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D783" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E783" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E784" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B785" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C785" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D785" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E785" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E786" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B787" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C787" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D787" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E787" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E788" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B789" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C789" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D789" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E789" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B791" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C791" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D791" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B793" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C793" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D793" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B795" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C795" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D795" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E795" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E796" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C797" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D797" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E797" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E798" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C799" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D799" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E800" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B801" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C801" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D801" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E801" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E802" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C803" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D803" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E803" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E804" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C805" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D805" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E805" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E806" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B807" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C807" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D807" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E807" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E808" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C809" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D809" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E809" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E810" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C811" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D811" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E811" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E812" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C813" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D813" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E813" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E814" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C815" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D815" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C817" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D817" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E817" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E818" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C819" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D819" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E819" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E820" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C821" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D821" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E821" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E822" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C823" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D823" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C825" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D825" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E825" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E826" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C827" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D827" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E827" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C829" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D829" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E829" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D831" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E831" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E832" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C833" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D833" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E833" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E834" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D835" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E835" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E836" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C837" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D837" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E837" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E838" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C839" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D839" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E839" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C841" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D841" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E841" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C843" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D843" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E843" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E844" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C845" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D845" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E845" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E846" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C847" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D847" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E847" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E848" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C849" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D849" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E849" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E850" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C851" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D851" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E851" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E852" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D853" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E853" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E854" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C855" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D855" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E855" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E856" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B857" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C857" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D857" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E857" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E858" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C859" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D859" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E859" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E860" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D861" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E861" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C863" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D863" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E863" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E864" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C865" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D865" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E865" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E866" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C867" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D867" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E867" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E868" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C869" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D869" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E869" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E870" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D871" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E871" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E872" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C873" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D873" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E873" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E874" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C875" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D875" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E875" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E876" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C877" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D877" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E877" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E878" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C879" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D879" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E879" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E880" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B881" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C881" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D881" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E881" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E882" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D883" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E883" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E884" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C885" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D885" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E885" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23011,7 +30707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23567,6 +31263,119 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2382</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history.xlsx
+++ b/history.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI53"/>
+  <dimension ref="A1:BI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7703,2619 +7703,6 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>921</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC41" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE41" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF41" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC41" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" s="3" t="inlineStr"/>
-      <c r="BH41" s="3" t="inlineStr"/>
-      <c r="BI41" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>4078</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>4567</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="T42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="V42" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="W42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y42" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="Z42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC42" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD42" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE42" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC42" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" s="2" t="inlineStr"/>
-      <c r="BH42" s="2" t="inlineStr"/>
-      <c r="BI42" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>4281</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>384</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC43" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD43" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE43" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC43" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" s="3" t="inlineStr"/>
-      <c r="BH43" s="3" t="inlineStr"/>
-      <c r="BI43" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>3334</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>126</v>
-      </c>
-      <c r="V44" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="W44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y44" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="Z44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD44" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE44" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC44" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG44" s="2" t="inlineStr"/>
-      <c r="BH44" s="2" t="inlineStr"/>
-      <c r="BI44" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>778</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC45" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD45" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE45" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF45" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA45" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BB45" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BC45" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BD45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BF45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" s="3" t="inlineStr"/>
-      <c r="BH45" s="3" t="inlineStr"/>
-      <c r="BI45" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>3491</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>2418</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V46" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="W46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y46" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC46" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD46" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE46" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF46" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC46" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" s="2" t="inlineStr"/>
-      <c r="BH46" s="2" t="inlineStr"/>
-      <c r="BI46" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>4676</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>2072</v>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="T47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="V47" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="W47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y47" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="Z47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC47" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD47" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE47" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF47" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ47" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC47" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG47" s="3" t="inlineStr"/>
-      <c r="BH47" s="3" t="inlineStr"/>
-      <c r="BI47" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>5867</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="V48" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y48" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC48" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD48" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE48" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF48" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC48" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" s="2" t="inlineStr"/>
-      <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1342</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>729</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="T49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="V49" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="W49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y49" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC49" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD49" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE49" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF49" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ49" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC49" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG49" s="3" t="inlineStr"/>
-      <c r="BH49" s="3" t="inlineStr"/>
-      <c r="BI49" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>5883</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>568</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>2149</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="T50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="V50" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="W50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y50" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB50" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD50" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE50" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF50" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC50" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG50" s="2" t="inlineStr"/>
-      <c r="BH50" s="2" t="inlineStr"/>
-      <c r="BI50" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>3912</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>1244</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>1996</v>
-      </c>
-      <c r="M51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="T51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="W51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y51" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB51" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC51" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD51" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE51" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF51" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC51" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" s="3" t="inlineStr"/>
-      <c r="BH51" s="3" t="inlineStr"/>
-      <c r="BI51" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>4400</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="T52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="V52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="W52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y52" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC52" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD52" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE52" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF52" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" s="2" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA52" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB52" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC52" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG52" s="2" t="inlineStr"/>
-      <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>2950</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="M53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="T53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="V53" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="W53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y53" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="Z53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB53" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC53" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="AD53" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE53" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF53" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AL53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AO53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AR53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="AX53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="3" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="BA53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC53" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BD53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG53" s="3" t="inlineStr"/>
-      <c r="BH53" s="3" t="inlineStr"/>
-      <c r="BI53" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10327,7 +7714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E885"/>
+  <dimension ref="A1:E664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25613,5089 +23000,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B665" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C665" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D665" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E665" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B666" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C666" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D666" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E666" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B667" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C667" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D667" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E667" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B668" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C668" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D668" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E668" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B669" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C669" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D669" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E669" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B670" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C670" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D670" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E670" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B671" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C671" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D671" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E671" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B672" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C672" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D672" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E672" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B673" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C673" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D673" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E673" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B674" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C674" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D674" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E674" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B675" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C675" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D675" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E675" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B676" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C676" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D676" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E676" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B677" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C677" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D677" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E677" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B678" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C678" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D678" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E678" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B679" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C679" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D679" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E679" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B680" s="2" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C680" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D680" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E680" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B681" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C681" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D681" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E681" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B682" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C682" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D682" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E682" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B683" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C683" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D683" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E683" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B684" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C684" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D684" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E684" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B685" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C685" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D685" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E685" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B686" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C686" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D686" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E686" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B687" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C687" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D687" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E687" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B688" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C688" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D688" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E688" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B689" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C689" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D689" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E689" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B690" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C690" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D690" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E690" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B691" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C691" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D691" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E691" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B692" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C692" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D692" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E692" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B693" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C693" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D693" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E693" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B694" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C694" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D694" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E694" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B695" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C695" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D695" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E695" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B696" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C696" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D696" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E696" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B697" s="3" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C697" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D697" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E697" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B698" s="2" t="inlineStr">
-        <is>
-          <t>CJ</t>
-        </is>
-      </c>
-      <c r="C698" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D698" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E698" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B699" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C699" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D699" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E699" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B700" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C700" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D700" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E700" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B701" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C701" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D701" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E701" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B702" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C702" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D702" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E702" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B703" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C703" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D703" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E703" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B704" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C704" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D704" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E704" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B705" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C705" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D705" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E705" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B706" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C706" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D706" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E706" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B707" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C707" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D707" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E707" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B708" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C708" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D708" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E708" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B709" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C709" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D709" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E709" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B710" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C710" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D710" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E710" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B711" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C711" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D711" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E711" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="712">
-      <c r="A712" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B712" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C712" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D712" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E712" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="713">
-      <c r="A713" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B713" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C713" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D713" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E713" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="714">
-      <c r="A714" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B714" s="2" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C714" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D714" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E714" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="715">
-      <c r="A715" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B715" s="3" t="inlineStr">
-        <is>
-          <t>JACKY</t>
-        </is>
-      </c>
-      <c r="C715" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D715" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E715" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="716">
-      <c r="A716" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B716" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C716" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D716" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E716" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="717">
-      <c r="A717" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B717" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C717" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D717" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E717" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="718">
-      <c r="A718" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B718" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C718" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D718" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E718" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719">
-      <c r="A719" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B719" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C719" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D719" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E719" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B720" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C720" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D720" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E720" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B721" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C721" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D721" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E721" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B722" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C722" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D722" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E722" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B723" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C723" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D723" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E723" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="724">
-      <c r="A724" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B724" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C724" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D724" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E724" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="725">
-      <c r="A725" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B725" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C725" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D725" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E725" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="726">
-      <c r="A726" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B726" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C726" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D726" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E726" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="727">
-      <c r="A727" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B727" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C727" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D727" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E727" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="728">
-      <c r="A728" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B728" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C728" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D728" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E728" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="729">
-      <c r="A729" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B729" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C729" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D729" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E729" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="730">
-      <c r="A730" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B730" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C730" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D730" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E730" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="731">
-      <c r="A731" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B731" s="3" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C731" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D731" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E731" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="732">
-      <c r="A732" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B732" s="2" t="inlineStr">
-        <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="C732" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D732" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E732" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="733">
-      <c r="A733" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B733" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C733" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D733" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E733" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="734">
-      <c r="A734" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B734" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C734" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D734" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E734" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="735">
-      <c r="A735" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B735" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C735" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D735" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E735" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="736">
-      <c r="A736" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B736" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C736" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D736" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E736" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="737">
-      <c r="A737" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B737" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C737" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D737" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E737" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="738">
-      <c r="A738" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B738" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C738" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D738" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E738" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="739">
-      <c r="A739" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B739" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C739" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D739" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E739" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="740">
-      <c r="A740" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B740" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C740" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D740" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E740" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="741">
-      <c r="A741" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B741" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C741" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D741" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E741" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="742">
-      <c r="A742" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B742" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C742" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D742" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E742" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="743">
-      <c r="A743" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B743" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C743" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D743" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E743" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B744" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C744" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D744" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E744" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B745" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C745" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D745" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E745" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="746">
-      <c r="A746" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B746" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C746" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D746" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E746" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="747">
-      <c r="A747" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B747" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C747" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D747" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E747" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="748">
-      <c r="A748" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B748" s="2" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C748" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D748" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E748" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="749">
-      <c r="A749" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B749" s="3" t="inlineStr">
-        <is>
-          <t>JW</t>
-        </is>
-      </c>
-      <c r="C749" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D749" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E749" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="750">
-      <c r="A750" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B750" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C750" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D750" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E750" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="751">
-      <c r="A751" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B751" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C751" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D751" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E751" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="752">
-      <c r="A752" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B752" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C752" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D752" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E752" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="753">
-      <c r="A753" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B753" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C753" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D753" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E753" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="754">
-      <c r="A754" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B754" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C754" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D754" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E754" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755">
-      <c r="A755" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B755" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C755" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D755" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E755" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="756">
-      <c r="A756" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B756" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C756" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D756" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E756" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="757">
-      <c r="A757" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B757" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C757" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D757" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E757" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="758">
-      <c r="A758" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B758" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C758" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D758" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E758" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="759">
-      <c r="A759" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B759" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C759" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D759" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E759" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="760">
-      <c r="A760" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B760" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C760" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D760" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E760" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B761" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C761" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D761" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E761" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="762">
-      <c r="A762" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B762" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C762" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D762" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E762" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="763">
-      <c r="A763" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B763" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C763" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D763" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E763" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="764">
-      <c r="A764" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B764" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C764" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D764" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E764" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="765">
-      <c r="A765" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B765" s="3" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C765" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D765" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E765" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="766">
-      <c r="A766" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B766" s="2" t="inlineStr">
-        <is>
-          <t>KEAN</t>
-        </is>
-      </c>
-      <c r="C766" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D766" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E766" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="767">
-      <c r="A767" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B767" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C767" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D767" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E767" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768">
-      <c r="A768" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B768" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C768" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D768" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E768" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="769">
-      <c r="A769" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B769" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C769" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D769" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E769" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="770">
-      <c r="A770" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B770" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C770" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D770" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E770" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="771">
-      <c r="A771" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B771" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C771" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D771" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E771" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="772">
-      <c r="A772" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B772" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C772" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D772" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E772" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773">
-      <c r="A773" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B773" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C773" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D773" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E773" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B774" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C774" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D774" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E774" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="775">
-      <c r="A775" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B775" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C775" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D775" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E775" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="776">
-      <c r="A776" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B776" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C776" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D776" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E776" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="777">
-      <c r="A777" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B777" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C777" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D777" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E777" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="778">
-      <c r="A778" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B778" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C778" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D778" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E778" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="779">
-      <c r="A779" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B779" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C779" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D779" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E779" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="780">
-      <c r="A780" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B780" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C780" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D780" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E780" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="781">
-      <c r="A781" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B781" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C781" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D781" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E781" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="782">
-      <c r="A782" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B782" s="2" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C782" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D782" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E782" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B783" s="3" t="inlineStr">
-        <is>
-          <t>KEE</t>
-        </is>
-      </c>
-      <c r="C783" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D783" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E783" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="784">
-      <c r="A784" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B784" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C784" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D784" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E784" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="785">
-      <c r="A785" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B785" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C785" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D785" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E785" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="786">
-      <c r="A786" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B786" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C786" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D786" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E786" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="787">
-      <c r="A787" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B787" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C787" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D787" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E787" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B788" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C788" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D788" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E788" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="789">
-      <c r="A789" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B789" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C789" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D789" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E789" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="790">
-      <c r="A790" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B790" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C790" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D790" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E790" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="791">
-      <c r="A791" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B791" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C791" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D791" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E791" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B792" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C792" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D792" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E792" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B793" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C793" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D793" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E793" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B794" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C794" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D794" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E794" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="795">
-      <c r="A795" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B795" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C795" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D795" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E795" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B796" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C796" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D796" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E796" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="797">
-      <c r="A797" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B797" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C797" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D797" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E797" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="798">
-      <c r="A798" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B798" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C798" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D798" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E798" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="799">
-      <c r="A799" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B799" s="3" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C799" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D799" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E799" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="800">
-      <c r="A800" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B800" s="2" t="inlineStr">
-        <is>
-          <t>KF</t>
-        </is>
-      </c>
-      <c r="C800" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D800" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E800" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="801">
-      <c r="A801" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B801" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C801" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D801" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E801" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="802">
-      <c r="A802" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B802" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C802" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D802" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E802" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="803">
-      <c r="A803" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B803" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C803" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D803" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E803" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="804">
-      <c r="A804" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B804" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C804" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D804" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E804" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="805">
-      <c r="A805" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B805" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C805" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D805" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E805" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="806">
-      <c r="A806" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B806" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C806" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D806" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E806" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="807">
-      <c r="A807" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B807" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C807" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D807" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E807" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="808">
-      <c r="A808" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B808" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C808" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D808" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E808" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="809">
-      <c r="A809" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B809" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C809" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D809" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E809" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B810" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C810" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D810" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E810" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B811" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C811" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D811" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E811" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B812" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C812" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D812" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E812" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B813" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C813" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D813" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E813" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B814" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C814" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D814" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E814" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B815" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C815" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D815" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E815" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B816" s="2" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C816" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D816" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E816" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B817" s="3" t="inlineStr">
-        <is>
-          <t>KI-MI</t>
-        </is>
-      </c>
-      <c r="C817" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D817" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E817" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B818" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C818" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D818" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E818" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="819">
-      <c r="A819" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B819" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C819" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D819" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E819" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B820" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C820" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D820" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E820" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B821" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C821" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D821" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E821" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B822" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C822" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D822" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E822" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B823" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C823" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D823" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E823" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B824" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C824" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D824" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E824" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="825">
-      <c r="A825" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B825" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C825" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D825" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E825" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="826">
-      <c r="A826" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B826" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C826" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D826" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E826" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="827">
-      <c r="A827" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B827" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C827" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D827" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E827" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828">
-      <c r="A828" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B828" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C828" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D828" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E828" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="829">
-      <c r="A829" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B829" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C829" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D829" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E829" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B830" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C830" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D830" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E830" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B831" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C831" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D831" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E831" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B832" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C832" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D832" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E832" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B833" s="3" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C833" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D833" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E833" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="834">
-      <c r="A834" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B834" s="2" t="inlineStr">
-        <is>
-          <t>KW</t>
-        </is>
-      </c>
-      <c r="C834" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D834" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E834" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="835">
-      <c r="A835" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B835" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C835" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D835" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E835" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="836">
-      <c r="A836" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B836" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C836" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D836" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E836" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B837" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C837" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D837" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E837" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B838" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C838" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D838" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E838" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B839" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C839" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D839" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E839" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B840" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C840" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D840" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E840" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B841" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C841" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D841" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E841" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B842" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C842" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D842" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E842" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B843" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C843" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D843" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E843" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B844" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C844" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D844" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E844" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B845" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C845" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D845" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E845" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="846">
-      <c r="A846" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B846" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C846" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D846" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E846" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="847">
-      <c r="A847" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B847" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C847" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D847" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E847" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="848">
-      <c r="A848" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B848" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C848" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D848" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E848" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="849">
-      <c r="A849" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B849" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C849" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D849" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E849" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="850">
-      <c r="A850" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B850" s="2" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C850" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D850" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E850" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="851">
-      <c r="A851" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B851" s="3" t="inlineStr">
-        <is>
-          <t>LEON</t>
-        </is>
-      </c>
-      <c r="C851" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D851" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E851" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="852">
-      <c r="A852" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B852" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C852" s="2" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D852" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E852" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="853">
-      <c r="A853" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B853" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C853" s="3" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D853" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E853" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="854">
-      <c r="A854" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B854" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C854" s="2" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D854" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E854" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="855">
-      <c r="A855" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B855" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C855" s="3" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D855" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E855" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="856">
-      <c r="A856" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B856" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C856" s="2" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D856" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E856" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="857">
-      <c r="A857" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B857" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C857" s="3" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D857" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E857" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B858" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C858" s="2" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D858" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E858" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="859">
-      <c r="A859" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B859" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C859" s="3" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D859" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E859" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="860">
-      <c r="A860" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B860" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C860" s="2" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D860" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E860" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="861">
-      <c r="A861" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B861" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C861" s="3" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D861" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E861" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="862">
-      <c r="A862" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B862" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C862" s="2" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D862" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E862" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863">
-      <c r="A863" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B863" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C863" s="3" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D863" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E863" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="864">
-      <c r="A864" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B864" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C864" s="2" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D864" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E864" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="865">
-      <c r="A865" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B865" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C865" s="3" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D865" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E865" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="866">
-      <c r="A866" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B866" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C866" s="2" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D866" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E866" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="867">
-      <c r="A867" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B867" s="3" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C867" s="3" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D867" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E867" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="868">
-      <c r="A868" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B868" s="2" t="inlineStr">
-        <is>
-          <t>NMK</t>
-        </is>
-      </c>
-      <c r="C868" s="2" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D868" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E868" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B869" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C869" s="3" t="inlineStr">
-        <is>
-          <t>CM-002</t>
-        </is>
-      </c>
-      <c r="D869" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E869" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="870">
-      <c r="A870" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B870" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C870" s="2" t="inlineStr">
-        <is>
-          <t>EVO</t>
-        </is>
-      </c>
-      <c r="D870" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E870" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="871">
-      <c r="A871" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B871" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C871" s="3" t="inlineStr">
-        <is>
-          <t>IMP-001</t>
-        </is>
-      </c>
-      <c r="D871" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E871" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="872">
-      <c r="A872" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B872" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C872" s="2" t="inlineStr">
-        <is>
-          <t>LF-002</t>
-        </is>
-      </c>
-      <c r="D872" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E872" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="873">
-      <c r="A873" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B873" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C873" s="3" t="inlineStr">
-        <is>
-          <t>TR-002</t>
-        </is>
-      </c>
-      <c r="D873" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E873" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="874">
-      <c r="A874" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B874" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C874" s="2" t="inlineStr">
-        <is>
-          <t>TR20</t>
-        </is>
-      </c>
-      <c r="D874" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E874" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="875">
-      <c r="A875" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B875" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C875" s="3" t="inlineStr">
-        <is>
-          <t>SKNR</t>
-        </is>
-      </c>
-      <c r="D875" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E875" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B876" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C876" s="2" t="inlineStr">
-        <is>
-          <t>SKNW</t>
-        </is>
-      </c>
-      <c r="D876" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E876" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B877" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C877" s="3" t="inlineStr">
-        <is>
-          <t>IFACE B</t>
-        </is>
-      </c>
-      <c r="D877" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E877" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B878" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C878" s="2" t="inlineStr">
-        <is>
-          <t>IFACE M</t>
-        </is>
-      </c>
-      <c r="D878" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E878" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="879">
-      <c r="A879" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B879" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C879" s="3" t="inlineStr">
-        <is>
-          <t>IFACE R</t>
-        </is>
-      </c>
-      <c r="D879" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E879" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B880" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C880" s="2" t="inlineStr">
-        <is>
-          <t>IFACE DB</t>
-        </is>
-      </c>
-      <c r="D880" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E880" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="881">
-      <c r="A881" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B881" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C881" s="3" t="inlineStr">
-        <is>
-          <t>BISON-G</t>
-        </is>
-      </c>
-      <c r="D881" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E881" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="882">
-      <c r="A882" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B882" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C882" s="2" t="inlineStr">
-        <is>
-          <t>BISON-M</t>
-        </is>
-      </c>
-      <c r="D882" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E882" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="883">
-      <c r="A883" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B883" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C883" s="3" t="inlineStr">
-        <is>
-          <t>BISON-R</t>
-        </is>
-      </c>
-      <c r="D883" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E883" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" s="2" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B884" s="2" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C884" s="2" t="inlineStr">
-        <is>
-          <t>LAM</t>
-        </is>
-      </c>
-      <c r="D884" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E884" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="B885" s="3" t="inlineStr">
-        <is>
-          <t>YI</t>
-        </is>
-      </c>
-      <c r="C885" s="3" t="inlineStr">
-        <is>
-          <t>LWM</t>
-        </is>
-      </c>
-      <c r="D885" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E885" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30707,7 +23011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31263,119 +23567,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2382</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>11000</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3" t="n">
-        <v>13500</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="3" t="n">
-        <v>2100</v>
-      </c>
-      <c r="AE5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="AH5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-01 22:50</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history.xlsx
+++ b/history.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SKU_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Team_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7703,6 +7703,2619 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>921</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC41" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE41" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF41" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC41" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" s="3" t="inlineStr"/>
+      <c r="BH41" s="3" t="inlineStr"/>
+      <c r="BI41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>4078</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>4567</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC42" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" s="2" t="inlineStr"/>
+      <c r="BH42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4281</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>384</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC43" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE43" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC43" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" s="3" t="inlineStr"/>
+      <c r="BH43" s="3" t="inlineStr"/>
+      <c r="BI43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>3334</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE44" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC44" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" s="2" t="inlineStr"/>
+      <c r="BH44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC45" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD45" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE45" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF45" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA45" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BB45" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BC45" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" s="3" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BF45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" s="3" t="inlineStr"/>
+      <c r="BH45" s="3" t="inlineStr"/>
+      <c r="BI45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>3491</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2418</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y46" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC46" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" s="2" t="inlineStr"/>
+      <c r="BH46" s="2" t="inlineStr"/>
+      <c r="BI46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>4676</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>2072</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC47" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD47" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE47" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC47" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" s="3" t="inlineStr"/>
+      <c r="BH47" s="3" t="inlineStr"/>
+      <c r="BI47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>5867</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y48" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE48" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC48" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" s="2" t="inlineStr"/>
+      <c r="BH48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>729</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD49" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE49" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ49" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC49" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG49" s="3" t="inlineStr"/>
+      <c r="BH49" s="3" t="inlineStr"/>
+      <c r="BI49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>5883</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>568</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y50" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC50" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD50" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC50" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" s="2" t="inlineStr"/>
+      <c r="BH50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>3912</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>1244</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC51" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD51" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE51" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF51" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC51" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" s="3" t="inlineStr"/>
+      <c r="BH51" s="3" t="inlineStr"/>
+      <c r="BI51" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y52" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC52" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="2" t="inlineStr"/>
+      <c r="BH52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD53" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE53" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC53" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" s="3" t="inlineStr"/>
+      <c r="BH53" s="3" t="inlineStr"/>
+      <c r="BI53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7714,7 +10327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E664"/>
+  <dimension ref="A1:E885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23000,6 +25613,5089 @@
         <v>0</v>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D665" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E665" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E666" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D667" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E667" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E668" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D669" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E670" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D671" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E672" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D673" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E673" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E674" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D675" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E675" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E676" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D677" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E677" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E678" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D679" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E679" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D681" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E682" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D683" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E684" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D685" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E685" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E686" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C687" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D687" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E687" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D689" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E689" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E690" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D691" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E691" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E692" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B693" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C693" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D693" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E693" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E694" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B695" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C695" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D695" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E695" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E696" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B697" s="3" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C697" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D697" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E697" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>CJ</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E698" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B699" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C699" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D699" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E699" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E700" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B701" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C701" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D701" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E701" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E702" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B703" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C703" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D703" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E703" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E704" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B705" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C705" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D705" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E706" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C707" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D707" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E707" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E708" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C709" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D709" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E710" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C711" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D711" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E711" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E712" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C713" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D713" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E713" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E714" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B715" s="3" t="inlineStr">
+        <is>
+          <t>JACKY</t>
+        </is>
+      </c>
+      <c r="C715" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D715" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E715" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B717" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C717" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D717" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E717" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E718" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B719" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D719" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E719" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E720" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B721" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C721" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D721" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E721" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C722" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D722" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E722" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D723" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E723" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C724" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D724" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B725" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D725" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C726" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D726" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B727" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D727" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C728" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D728" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C729" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D729" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E729" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C730" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D730" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D731" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="C732" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D732" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C733" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D733" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C734" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D734" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E734" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C735" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D735" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C736" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D736" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B737" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C737" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D737" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C738" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D738" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B739" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C739" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D739" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E739" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C740" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D740" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E740" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B741" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D741" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E741" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C742" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D742" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B743" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C743" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D743" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C744" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D744" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B745" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C745" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D745" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C746" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D746" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D747" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B749" s="3" t="inlineStr">
+        <is>
+          <t>JW</t>
+        </is>
+      </c>
+      <c r="C749" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D749" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C751" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D751" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C753" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D753" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E753" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E754" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C755" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D755" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E755" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D756" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E756" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B757" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C757" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D757" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C758" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D758" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B759" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C759" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D759" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C760" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D760" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B761" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C761" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D761" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E761" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C762" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D762" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E762" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B763" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C763" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D763" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E763" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B764" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C764" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D764" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E764" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B765" s="3" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C765" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D765" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E765" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B766" s="2" t="inlineStr">
+        <is>
+          <t>KEAN</t>
+        </is>
+      </c>
+      <c r="C766" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D766" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B767" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C767" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D767" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B768" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C768" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D768" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B769" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C769" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D769" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B770" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C770" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D770" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B771" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C771" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D771" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C772" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D772" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E772" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B773" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C773" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D773" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B774" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C774" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D774" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B775" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C775" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D775" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E775" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B776" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C776" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D776" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E776" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B777" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C777" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D777" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E777" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B778" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C778" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D778" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E778" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C779" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D779" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E779" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B780" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C780" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D780" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E780" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B781" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C781" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D781" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B782" s="2" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C782" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D782" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B783" s="3" t="inlineStr">
+        <is>
+          <t>KEE</t>
+        </is>
+      </c>
+      <c r="C783" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D783" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E783" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B784" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C784" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D784" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E784" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B785" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C785" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D785" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E785" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B786" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C786" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D786" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E786" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B787" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C787" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D787" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E787" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B788" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C788" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D788" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E788" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B789" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C789" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D789" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E789" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B790" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C790" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D790" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B791" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C791" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D791" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B792" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C792" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D792" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B793" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C793" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D793" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C794" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D794" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B795" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C795" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D795" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E795" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B796" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C796" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D796" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E796" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C797" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D797" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E797" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B798" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C798" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D798" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E798" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C799" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D799" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B800" s="2" t="inlineStr">
+        <is>
+          <t>KF</t>
+        </is>
+      </c>
+      <c r="C800" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D800" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E800" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B801" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C801" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D801" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E801" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B802" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C802" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D802" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E802" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B803" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C803" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D803" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E803" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B804" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C804" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D804" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E804" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B805" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C805" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D805" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E805" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B806" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C806" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D806" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E806" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B807" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C807" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D807" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E807" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B808" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C808" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D808" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E808" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B809" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C809" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D809" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E809" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E810" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B811" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C811" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D811" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E811" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E812" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B813" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C813" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D813" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E813" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E814" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B815" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C815" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D815" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>KI-MI</t>
+        </is>
+      </c>
+      <c r="C817" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D817" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E817" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E818" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C819" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D819" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E819" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E820" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C821" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D821" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E821" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E822" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C823" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D823" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B825" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C825" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D825" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E825" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E826" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B827" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C827" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D827" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E827" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E828" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B829" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C829" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D829" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E829" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E830" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B831" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C831" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D831" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E831" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E832" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B833" s="3" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C833" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D833" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E833" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>KW</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E834" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B835" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C835" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D835" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E835" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E836" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B837" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C837" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D837" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E837" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E838" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C839" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D839" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E839" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C841" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D841" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E841" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C843" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D843" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E843" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E844" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C845" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D845" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E845" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E846" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B847" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C847" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D847" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E847" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E848" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B849" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C849" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D849" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E849" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E850" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B851" s="3" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="C851" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D851" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E851" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E852" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B853" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C853" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D853" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E853" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E854" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B855" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C855" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D855" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E855" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E856" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B857" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C857" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D857" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E857" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E858" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B859" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C859" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D859" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E859" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E860" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C861" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D861" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E861" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C863" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D863" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E863" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E864" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C865" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D865" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E865" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E866" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C867" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D867" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E867" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>NMK</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E868" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B869" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C869" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D869" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E869" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E870" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B871" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C871" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D871" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E871" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E872" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B873" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C873" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D873" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E873" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E874" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B875" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C875" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D875" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E875" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E876" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B877" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C877" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D877" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E877" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E878" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B879" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C879" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D879" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E879" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E880" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B881" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C881" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D881" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E881" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E882" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C883" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D883" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E883" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E884" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>YI</t>
+        </is>
+      </c>
+      <c r="C885" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D885" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E885" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23011,7 +30707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23567,6 +31263,119 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2382</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>13500</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="3" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="AH5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01 22:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history.xlsx
+++ b/history.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI53"/>
+  <dimension ref="A1:BI54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10316,6 +10316,207 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE54" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF54" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="2" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" s="2" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="BC54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" s="2" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="BE54" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="BF54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" s="2" t="inlineStr"/>
+      <c r="BH54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10327,7 +10528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E885"/>
+  <dimension ref="A1:E902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30694,6 +30895,397 @@
       </c>
       <c r="E885" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E886" s="2" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C887" s="3" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D887" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E887" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E888" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B889" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C889" s="3" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D889" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E889" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E890" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C891" s="3" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D891" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E891" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E892" s="2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B893" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C893" s="3" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D893" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E893" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E894" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B895" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C895" s="3" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D895" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E895" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E896" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B897" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C897" s="3" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D897" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E897" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E898" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B899" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C899" s="3" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D899" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E899" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E900" s="2" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="3" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B901" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C901" s="3" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D901" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E901" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E902" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/history.xlsx
+++ b/history.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI54"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10517,6 +10517,207 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD55" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE55" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF55" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AL55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="3" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="BA55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" s="3" t="inlineStr"/>
+      <c r="BH55" s="3" t="inlineStr"/>
+      <c r="BI55" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-14 13:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10528,7 +10729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E902"/>
+  <dimension ref="A1:E919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -31286,6 +31487,397 @@
       </c>
       <c r="E902" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B903" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C903" s="3" t="inlineStr">
+        <is>
+          <t>CM-002</t>
+        </is>
+      </c>
+      <c r="D903" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E903" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>EVO</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E904" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B905" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C905" s="3" t="inlineStr">
+        <is>
+          <t>IMP-001</t>
+        </is>
+      </c>
+      <c r="D905" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E905" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>LF-002</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E906" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B907" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C907" s="3" t="inlineStr">
+        <is>
+          <t>TR-002</t>
+        </is>
+      </c>
+      <c r="D907" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E907" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>TR20</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E908" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B909" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C909" s="3" t="inlineStr">
+        <is>
+          <t>SKNR</t>
+        </is>
+      </c>
+      <c r="D909" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E909" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>SKNW</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E910" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B911" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C911" s="3" t="inlineStr">
+        <is>
+          <t>IFACE B</t>
+        </is>
+      </c>
+      <c r="D911" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E911" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>IFACE M</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E912" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B913" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C913" s="3" t="inlineStr">
+        <is>
+          <t>IFACE R</t>
+        </is>
+      </c>
+      <c r="D913" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E913" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>IFACE DB</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E914" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B915" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C915" s="3" t="inlineStr">
+        <is>
+          <t>BISON-G</t>
+        </is>
+      </c>
+      <c r="D915" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E915" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>BISON-M</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E916" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B917" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C917" s="3" t="inlineStr">
+        <is>
+          <t>BISON-R</t>
+        </is>
+      </c>
+      <c r="D917" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E917" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E918" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="3" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B919" s="3" t="inlineStr">
+        <is>
+          <t>SAM</t>
+        </is>
+      </c>
+      <c r="C919" s="3" t="inlineStr">
+        <is>
+          <t>LWM</t>
+        </is>
+      </c>
+      <c r="D919" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E919" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
